--- a/artfynd/A 10525-2024 artfynd.xlsx
+++ b/artfynd/A 10525-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60457743</v>
+        <v>60457754</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630487.7442488786</v>
+        <v>630488</v>
       </c>
       <c r="R2" t="n">
-        <v>7337601.263572228</v>
+        <v>7337601</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,19 +746,9 @@
           <t>2016-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60457754</v>
+        <v>60457669</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -838,14 +818,14 @@
       <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Bergnäsvägen, bäckdråg, Pi lm</t>
+          <t>Vägkant vid Sakkaträsket, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>630487.7442488786</v>
+        <v>630536</v>
       </c>
       <c r="R3" t="n">
-        <v>7337601.263572228</v>
+        <v>7338144</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,19 +855,9 @@
           <t>2016-07-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-07-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +871,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>bäckdråg</t>
+          <t>dike</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -923,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60457719</v>
+        <v>60457743</v>
       </c>
       <c r="B4" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>630487.7442488786</v>
+        <v>630488</v>
       </c>
       <c r="R4" t="n">
-        <v>7337601.263572228</v>
+        <v>7337601</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,19 +964,9 @@
           <t>2016-07-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-07-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,6 +995,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Pite lappmarks flora (2007-2018)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>60457719</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra Bergnäsvägen, bäckdråg, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>630488</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7337601</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-07-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-07-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>bäckdråg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elisabet Arvidson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>

--- a/artfynd/A 10525-2024 artfynd.xlsx
+++ b/artfynd/A 10525-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -781,6 +786,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60457754</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60457669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60457743</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,8 +1128,19 @@
           <t>Pite lappmarks flora (2007-2018)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60457719</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>